--- a/www/ig/fhir/core/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="466">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil se basant sur la ressource Medication Administration pour indiquer l'oxygène inhalé.</t>
+    <t>Profile based on the MedicationAdministration resource to indicate inhaled oxygen. This profile makes it possible to complement the information from the Oxygen Saturation Observation resource with oxygen intake provided through mechanical ventilation.
+Profil se basant sur la ressource Medication Administration pour indiquer l'oxygène inhalé. Ce profil permet de compléter les informations de la ressource Observation saturation en oxygène avec les apports d'oxygène via une ventilation mécanique.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationAdministration</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationAdministration|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -426,7 +427,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -439,14 +440,14 @@
     <t>MedicationAdministration.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -468,6 +469,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-medication-administration-inhaled-oxygen|2.2.0</t>
+  </si>
+  <si>
     <t>MedicationAdministration.meta.security</t>
   </si>
   <si>
@@ -490,7 +494,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -514,7 +518,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -557,7 +561,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -683,7 +687,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -748,7 +752,7 @@
     <t>A set of codes indicating the reason why the MedicationAdministration is negated.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -772,7 +776,7 @@
     <t>A coded concept describing where the medication administered is expected to occur.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -793,7 +797,7 @@
     <t>Codes identifying substance or product that can be administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -992,7 +996,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1017,7 +1021,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1042,7 +1046,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1140,7 +1144,7 @@
     <t>A code describing the role an individual played in administering the medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1152,7 +1156,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|Device|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1180,7 +1184,7 @@
     <t>A set of codes indicating the reason why the MedicationAdministration was made.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1195,7 +1199,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1223,7 +1227,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1248,7 +1252,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1337,7 +1341,7 @@
     <t>A coded concept describing the site location the medicine enters into or onto the body.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1358,7 +1362,7 @@
     <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1382,7 +1386,7 @@
     <t>A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1394,7 +1398,7 @@
     <t>MedicationAdministration.dosage.dose</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1417,7 +1421,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>Dose quantity per unit of time</t>
@@ -1438,7 +1442,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1764,17 +1768,17 @@
   <dimension ref="A1:AO63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.08984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.08984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.89453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.51953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.51953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.2578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="161.8203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="162.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1783,27 +1787,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="120.9609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.1875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="104.34375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.5078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.5625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="100.58203125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="20.3125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="237.45703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="86.76171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="17.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3028,7 +3032,7 @@
         <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>79</v>
@@ -3099,10 +3103,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3125,16 +3129,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3160,13 +3164,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -3184,7 +3188,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3216,10 +3220,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3242,16 +3246,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3277,13 +3281,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3301,7 +3305,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3333,10 +3337,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3362,13 +3366,13 @@
         <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3418,7 +3422,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3450,10 +3454,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3476,16 +3480,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3511,13 +3515,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -3535,7 +3539,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3567,14 +3571,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3593,16 +3597,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3652,7 +3656,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3670,7 +3674,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3684,14 +3688,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3710,16 +3714,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3769,7 +3773,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3787,7 +3791,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3801,10 +3805,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3833,7 +3837,7 @@
         <v>111</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>113</v>
@@ -3886,7 +3890,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3904,7 +3908,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3918,10 +3922,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3947,16 +3951,16 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4005,7 +4009,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4023,7 +4027,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4037,10 +4041,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4063,16 +4067,16 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4122,7 +4126,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4137,13 +4141,13 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>79</v>
@@ -4154,10 +4158,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4183,10 +4187,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4237,7 +4241,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4252,10 +4256,10 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4269,10 +4273,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4295,13 +4299,13 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4352,7 +4356,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4367,10 +4371,10 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4384,10 +4388,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4410,16 +4414,16 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4445,13 +4449,13 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4469,7 +4473,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -4484,16 +4488,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4501,10 +4505,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4527,13 +4531,13 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4560,13 +4564,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4584,7 +4588,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4599,16 +4603,16 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4616,10 +4620,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4642,13 +4646,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4675,13 +4679,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4699,7 +4703,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4717,7 +4721,7 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4731,10 +4735,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4757,16 +4761,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4792,13 +4796,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4816,7 +4820,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -4831,16 +4835,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4848,10 +4852,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4963,10 +4967,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5080,10 +5084,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5106,19 +5110,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5167,7 +5171,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5185,13 +5189,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5199,10 +5203,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5314,10 +5318,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5431,10 +5435,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5460,23 +5464,23 @@
         <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>79</v>
@@ -5518,7 +5522,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5536,13 +5540,13 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5550,10 +5554,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5579,13 +5583,13 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5635,7 +5639,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5653,13 +5657,13 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5667,10 +5671,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5693,24 +5697,24 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>79</v>
@@ -5752,7 +5756,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5770,13 +5774,13 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5784,10 +5788,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5813,14 +5817,14 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5869,7 +5873,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5887,13 +5891,13 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -5901,10 +5905,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5927,19 +5931,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5988,7 +5992,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6006,13 +6010,13 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6020,10 +6024,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6049,16 +6053,16 @@
         <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6107,7 +6111,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6125,13 +6129,13 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6139,10 +6143,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6165,13 +6169,13 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6222,7 +6226,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -6237,16 +6241,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6254,10 +6258,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6280,13 +6284,13 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6337,7 +6341,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6352,16 +6356,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6369,10 +6373,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6395,13 +6399,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6452,7 +6456,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6470,10 +6474,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6484,10 +6488,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6510,13 +6514,13 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6567,7 +6571,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>89</v>
@@ -6582,16 +6586,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6599,10 +6603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6625,13 +6629,13 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6682,7 +6686,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6697,16 +6701,16 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6714,10 +6718,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6829,10 +6833,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6946,14 +6950,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6975,16 +6979,16 @@
         <v>110</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7033,7 +7037,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7051,7 +7055,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7065,10 +7069,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7091,13 +7095,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7124,13 +7128,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7148,7 +7152,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7163,10 +7167,10 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7180,10 +7184,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7206,13 +7210,13 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7263,7 +7267,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>89</v>
@@ -7278,10 +7282,10 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7295,10 +7299,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7321,13 +7325,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7354,13 +7358,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7378,7 +7382,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7393,16 +7397,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7410,10 +7414,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7436,16 +7440,16 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7495,7 +7499,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7510,27 +7514,27 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7553,16 +7557,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7612,7 +7616,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7627,16 +7631,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7644,10 +7648,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7670,13 +7674,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7727,7 +7731,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7745,13 +7749,13 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7759,10 +7763,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7785,13 +7789,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7842,7 +7846,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7857,10 +7861,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7874,10 +7878,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7900,13 +7904,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7957,7 +7961,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7969,13 +7973,13 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -7989,10 +7993,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8104,10 +8108,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8221,14 +8225,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8250,16 +8254,16 @@
         <v>110</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8308,7 +8312,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8326,7 +8330,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8340,10 +8344,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8369,10 +8373,10 @@
         <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8423,7 +8427,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8441,7 +8445,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8455,10 +8459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8481,16 +8485,16 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8516,13 +8520,13 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -8540,7 +8544,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8558,13 +8562,13 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8572,10 +8576,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8598,13 +8602,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8631,13 +8635,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -8655,7 +8659,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8673,13 +8677,13 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -8687,10 +8691,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8713,16 +8717,16 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8748,13 +8752,13 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -8772,7 +8776,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8790,13 +8794,13 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -8804,10 +8808,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8830,16 +8834,16 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8889,7 +8893,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8907,13 +8911,13 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -8921,10 +8925,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8947,16 +8951,16 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9006,7 +9010,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9024,13 +9028,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9038,10 +9042,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9064,16 +9068,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9123,7 +9127,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9141,7 +9145,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,8 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile based on the MedicationAdministration resource to indicate inhaled oxygen. This profile makes it possible to complement the information from the Oxygen Saturation Observation resource with oxygen intake provided through mechanical ventilation.
-Profil se basant sur la ressource Medication Administration pour indiquer l'oxygène inhalé. Ce profil permet de compléter les informations de la ressource Observation saturation en oxygène avec les apports d'oxygène via une ventilation mécanique.</t>
+    <t>Profil se basant sur la ressource Medication Administration pour indiquer l'oxygène inhalé.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -115,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationAdministration|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationAdministration</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -427,7 +426,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -440,14 +439,14 @@
     <t>MedicationAdministration.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -469,9 +468,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-medication-administration-inhaled-oxygen|2.2.0</t>
-  </si>
-  <si>
     <t>MedicationAdministration.meta.security</t>
   </si>
   <si>
@@ -494,7 +490,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -518,7 +514,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -561,7 +557,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -687,7 +683,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
+    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
 </t>
   </si>
   <si>
@@ -752,7 +748,7 @@
     <t>A set of codes indicating the reason why the MedicationAdministration is negated.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -776,7 +772,7 @@
     <t>A coded concept describing where the medication administered is expected to occur.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -797,7 +793,7 @@
     <t>Codes identifying substance or product that can be administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -996,7 +992,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1021,7 +1017,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
+    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
 </t>
   </si>
   <si>
@@ -1046,7 +1042,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1144,7 +1140,7 @@
     <t>A code describing the role an individual played in administering the medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1156,7 +1152,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|Device|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
+    <t xml:space="preserve">Reference(RelatedPerson|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1184,7 +1180,7 @@
     <t>A set of codes indicating the reason why the MedicationAdministration was made.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1199,7 +1195,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
 </t>
   </si>
   <si>
@@ -1227,7 +1223,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
+    <t xml:space="preserve">Reference(MedicationRequest)
 </t>
   </si>
   <si>
@@ -1252,7 +1248,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(Device)
 </t>
   </si>
   <si>
@@ -1341,7 +1337,7 @@
     <t>A coded concept describing the site location the medicine enters into or onto the body.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1362,7 +1358,7 @@
     <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1386,7 +1382,7 @@
     <t>A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1398,7 +1394,7 @@
     <t>MedicationAdministration.dosage.dose</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1421,7 +1417,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity|4.0.1}</t>
+Quantity {SimpleQuantity}</t>
   </si>
   <si>
     <t>Dose quantity per unit of time</t>
@@ -1442,7 +1438,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1)
+    <t xml:space="preserve">Reference(Provenance)
 </t>
   </si>
   <si>
@@ -1768,17 +1764,17 @@
   <dimension ref="A1:AO63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.51953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.51953125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.2578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.08984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="55.08984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.89453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="162.546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="161.8203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1787,27 +1783,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="104.34375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.5078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.5625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="120.9609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.1875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="44.703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="237.45703125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="86.76171875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="17.5234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="100.58203125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="20.3125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3032,7 +3028,7 @@
         <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>79</v>
@@ -3103,10 +3099,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3129,16 +3125,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3164,31 +3160,31 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3220,10 +3216,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3246,16 +3242,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3281,31 +3277,31 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3337,10 +3333,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3366,13 +3362,13 @@
         <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3422,7 +3418,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3454,10 +3450,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3480,16 +3476,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3515,31 +3511,31 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3571,14 +3567,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3597,16 +3593,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3656,7 +3652,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3674,7 +3670,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3688,14 +3684,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3714,16 +3710,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3773,7 +3769,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3791,7 +3787,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3805,10 +3801,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3837,7 +3833,7 @@
         <v>111</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>113</v>
@@ -3890,7 +3886,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3908,7 +3904,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3922,10 +3918,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3951,16 +3947,16 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4009,7 +4005,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4027,7 +4023,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4041,10 +4037,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4067,16 +4063,16 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4126,7 +4122,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4141,13 +4137,13 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>79</v>
@@ -4158,10 +4154,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4187,10 +4183,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4241,7 +4237,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4256,10 +4252,10 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4273,10 +4269,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4299,13 +4295,13 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4356,7 +4352,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4371,10 +4367,10 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4388,10 +4384,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4414,16 +4410,16 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4449,14 +4445,14 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y23" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="Y23" t="s" s="2">
+      <c r="Z23" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4473,7 +4469,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -4488,16 +4484,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4505,10 +4501,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4531,13 +4527,13 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4564,14 +4560,14 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="Z24" t="s" s="2">
-        <v>237</v>
-      </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4588,7 +4584,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4603,16 +4599,16 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4620,10 +4616,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4646,13 +4642,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4679,14 +4675,14 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>245</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
       </c>
@@ -4703,7 +4699,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4721,7 +4717,7 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4735,10 +4731,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4761,16 +4757,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4796,14 +4792,14 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>252</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
       </c>
@@ -4820,7 +4816,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -4835,16 +4831,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4852,10 +4848,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4967,10 +4963,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5084,10 +5080,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5110,19 +5106,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5171,7 +5167,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5189,13 +5185,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5203,10 +5199,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5318,10 +5314,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5435,10 +5431,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5464,65 +5460,65 @@
         <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5540,13 +5536,13 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5554,10 +5550,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5583,13 +5579,13 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5639,7 +5635,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5657,13 +5653,13 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5671,10 +5667,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5697,66 +5693,66 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5774,13 +5770,13 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5788,10 +5784,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5817,14 +5813,14 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5873,7 +5869,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5891,13 +5887,13 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -5905,10 +5901,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5931,19 +5927,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5992,7 +5988,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6010,13 +6006,13 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6024,10 +6020,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6053,16 +6049,16 @@
         <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6111,7 +6107,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6129,13 +6125,13 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6143,10 +6139,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6169,13 +6165,13 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6226,7 +6222,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -6241,16 +6237,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6258,10 +6254,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6284,13 +6280,13 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6341,7 +6337,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6356,16 +6352,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6373,10 +6369,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6399,13 +6395,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6456,7 +6452,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6474,10 +6470,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6488,10 +6484,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6514,13 +6510,13 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6571,7 +6567,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>89</v>
@@ -6586,16 +6582,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6603,10 +6599,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6629,13 +6625,13 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6686,7 +6682,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6701,16 +6697,16 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6718,10 +6714,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6833,10 +6829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6950,14 +6946,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6979,16 +6975,16 @@
         <v>110</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7037,7 +7033,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7055,7 +7051,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7069,10 +7065,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7095,13 +7091,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7128,14 +7124,14 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7152,7 +7148,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7167,10 +7163,10 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7184,10 +7180,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7210,13 +7206,13 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7267,7 +7263,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>89</v>
@@ -7282,10 +7278,10 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7299,10 +7295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7325,13 +7321,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7358,14 +7354,14 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7382,7 +7378,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7397,16 +7393,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7414,10 +7410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7440,16 +7436,16 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7499,7 +7495,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7514,27 +7510,27 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>390</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7557,16 +7553,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7616,7 +7612,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7631,16 +7627,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7648,10 +7644,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7674,13 +7670,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7731,7 +7727,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7749,13 +7745,13 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7763,10 +7759,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7789,13 +7785,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7846,7 +7842,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7861,10 +7857,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7878,10 +7874,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7904,13 +7900,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7961,7 +7957,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7973,13 +7969,13 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -7993,10 +7989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8108,10 +8104,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8225,14 +8221,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8254,16 +8250,16 @@
         <v>110</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8312,7 +8308,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8330,7 +8326,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8344,10 +8340,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8373,10 +8369,10 @@
         <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8427,7 +8423,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8445,7 +8441,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8459,10 +8455,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8485,16 +8481,16 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8520,14 +8516,14 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>428</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8544,7 +8540,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8562,13 +8558,13 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8576,10 +8572,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8602,13 +8598,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8635,14 +8631,14 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>435</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8659,7 +8655,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8677,13 +8673,13 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -8691,10 +8687,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8717,16 +8713,16 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8752,14 +8748,14 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>443</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
       </c>
@@ -8776,7 +8772,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8794,13 +8790,13 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -8808,10 +8804,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8834,16 +8830,16 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8893,7 +8889,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8911,13 +8907,13 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -8925,10 +8921,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8951,16 +8947,16 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9010,7 +9006,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9028,13 +9024,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9042,10 +9038,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9068,16 +9064,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9127,7 +9123,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9145,7 +9141,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="466">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil se basant sur la ressource Medication Administration pour indiquer l'oxygène inhalé.</t>
+    <t>Profile based on the MedicationAdministration resource to indicate inhaled oxygen. This profile makes it possible to complement the information from the Oxygen Saturation Observation resource with oxygen intake provided through mechanical ventilation.
+Profil se basant sur la ressource Medication Administration pour indiquer l'oxygène inhalé. Ce profil permet de compléter les informations de la ressource Observation saturation en oxygène avec les apports d'oxygène via une ventilation mécanique.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationAdministration</t>
+    <t>http://hl7.org/fhir/StructureDefinition/MedicationAdministration|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -426,7 +427,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -439,14 +440,14 @@
     <t>MedicationAdministration.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -468,6 +469,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-medication-administration-inhaled-oxygen|2.2.0</t>
+  </si>
+  <si>
     <t>MedicationAdministration.meta.security</t>
   </si>
   <si>
@@ -490,7 +494,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -514,7 +518,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -557,7 +561,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -683,7 +687,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -748,7 +752,7 @@
     <t>A set of codes indicating the reason why the MedicationAdministration is negated.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -772,7 +776,7 @@
     <t>A coded concept describing where the medication administered is expected to occur.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -793,7 +797,7 @@
     <t>Codes identifying substance or product that can be administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -992,7 +996,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1017,7 +1021,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1042,7 +1046,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1140,7 +1144,7 @@
     <t>A code describing the role an individual played in administering the medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1152,7 +1156,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|Device|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|Device|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1180,7 +1184,7 @@
     <t>A set of codes indicating the reason why the MedicationAdministration was made.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1195,7 +1199,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1223,7 +1227,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1248,7 +1252,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1337,7 +1341,7 @@
     <t>A coded concept describing the site location the medicine enters into or onto the body.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1358,7 +1362,7 @@
     <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1382,7 +1386,7 @@
     <t>A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1394,7 +1398,7 @@
     <t>MedicationAdministration.dosage.dose</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1417,7 +1421,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>Dose quantity per unit of time</t>
@@ -1438,7 +1442,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1764,17 +1768,17 @@
   <dimension ref="A1:AO63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.08984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.08984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.89453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.51953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.51953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.2578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="161.8203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="162.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1783,27 +1787,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="120.9609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.1875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="104.34375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.5078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.5625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="100.58203125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="20.3125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="237.45703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="86.76171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="17.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3028,7 +3032,7 @@
         <v>79</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>79</v>
@@ -3099,10 +3103,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3125,16 +3129,16 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3160,13 +3164,13 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>79</v>
@@ -3184,7 +3188,7 @@
         <v>79</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3216,10 +3220,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3242,16 +3246,16 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3277,13 +3281,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3301,7 +3305,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3333,10 +3337,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3362,13 +3366,13 @@
         <v>131</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3418,7 +3422,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3450,10 +3454,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3476,16 +3480,16 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3511,13 +3515,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
@@ -3535,7 +3539,7 @@
         <v>79</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3567,14 +3571,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3593,16 +3597,16 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3652,7 +3656,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3670,7 +3674,7 @@
         <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>79</v>
@@ -3684,14 +3688,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3710,16 +3714,16 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3769,7 +3773,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3787,7 +3791,7 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
@@ -3801,10 +3805,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3833,7 +3837,7 @@
         <v>111</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>113</v>
@@ -3886,7 +3890,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3904,7 +3908,7 @@
         <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3918,10 +3922,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3947,16 +3951,16 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -4005,7 +4009,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4023,7 +4027,7 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>79</v>
@@ -4037,10 +4041,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4063,16 +4067,16 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4122,7 +4126,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4137,13 +4141,13 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>79</v>
@@ -4154,10 +4158,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4183,10 +4187,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4237,7 +4241,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4252,10 +4256,10 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -4269,10 +4273,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4295,13 +4299,13 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4352,7 +4356,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4367,10 +4371,10 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4384,10 +4388,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4410,16 +4414,16 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4445,13 +4449,13 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4469,7 +4473,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -4484,16 +4488,16 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4501,10 +4505,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4527,13 +4531,13 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4560,13 +4564,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4584,7 +4588,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4599,16 +4603,16 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>79</v>
@@ -4616,10 +4620,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4642,13 +4646,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4675,13 +4679,13 @@
         <v>79</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>79</v>
@@ -4699,7 +4703,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4717,7 +4721,7 @@
         <v>79</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4731,10 +4735,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4757,16 +4761,16 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4792,13 +4796,13 @@
         <v>79</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>79</v>
@@ -4816,7 +4820,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -4831,16 +4835,16 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4848,10 +4852,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4963,10 +4967,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5080,10 +5084,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5106,19 +5110,19 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5167,7 +5171,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5185,13 +5189,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5199,10 +5203,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5314,10 +5318,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5431,10 +5435,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5460,23 +5464,23 @@
         <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>79</v>
@@ -5518,7 +5522,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5536,13 +5540,13 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5550,10 +5554,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5579,13 +5583,13 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5635,7 +5639,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5653,13 +5657,13 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5667,10 +5671,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5693,24 +5697,24 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>79</v>
@@ -5752,7 +5756,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5770,13 +5774,13 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5784,10 +5788,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5813,14 +5817,14 @@
         <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5869,7 +5873,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5887,13 +5891,13 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -5901,10 +5905,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5927,19 +5931,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -5988,7 +5992,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6006,13 +6010,13 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6020,10 +6024,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6049,16 +6053,16 @@
         <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6107,7 +6111,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6125,13 +6129,13 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6139,10 +6143,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6165,13 +6169,13 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6222,7 +6226,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -6237,16 +6241,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6254,10 +6258,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6280,13 +6284,13 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6337,7 +6341,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6352,16 +6356,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6369,10 +6373,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6395,13 +6399,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6452,7 +6456,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6470,10 +6474,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6484,10 +6488,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6510,13 +6514,13 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6567,7 +6571,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>89</v>
@@ -6582,16 +6586,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6599,10 +6603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6625,13 +6629,13 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6682,7 +6686,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6697,16 +6701,16 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6714,10 +6718,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6829,10 +6833,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6946,14 +6950,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6975,16 +6979,16 @@
         <v>110</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7033,7 +7037,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7051,7 +7055,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -7065,10 +7069,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7091,13 +7095,13 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7124,13 +7128,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7148,7 +7152,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7163,10 +7167,10 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7180,10 +7184,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7206,13 +7210,13 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7263,7 +7267,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>89</v>
@@ -7278,10 +7282,10 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7295,10 +7299,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7321,13 +7325,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7354,13 +7358,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7378,7 +7382,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7393,16 +7397,16 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7410,10 +7414,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7436,16 +7440,16 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7495,7 +7499,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7510,27 +7514,27 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7553,16 +7557,16 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7612,7 +7616,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7627,16 +7631,16 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7644,10 +7648,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7670,13 +7674,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7727,7 +7731,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7745,13 +7749,13 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7759,10 +7763,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7785,13 +7789,13 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7842,7 +7846,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7857,10 +7861,10 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7874,10 +7878,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7900,13 +7904,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7957,7 +7961,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7969,13 +7973,13 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -7989,10 +7993,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8104,10 +8108,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8221,14 +8225,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8250,16 +8254,16 @@
         <v>110</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8308,7 +8312,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8326,7 +8330,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8340,10 +8344,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8369,10 +8373,10 @@
         <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8423,7 +8427,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8441,7 +8445,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8455,10 +8459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8481,16 +8485,16 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8516,13 +8520,13 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -8540,7 +8544,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8558,13 +8562,13 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -8572,10 +8576,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8598,13 +8602,13 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8631,13 +8635,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -8655,7 +8659,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8673,13 +8677,13 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -8687,10 +8691,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8713,16 +8717,16 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8748,13 +8752,13 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -8772,7 +8776,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8790,13 +8794,13 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -8804,10 +8808,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8830,16 +8834,16 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8889,7 +8893,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8907,13 +8911,13 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -8921,10 +8925,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8947,16 +8951,16 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9006,7 +9010,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9024,13 +9028,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9038,10 +9042,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9064,16 +9068,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9123,7 +9127,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9141,7 +9145,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
